--- a/output/user-access-review/claude/sample-1/workpaper.xlsx
+++ b/output/user-access-review/claude/sample-1/workpaper.xlsx
@@ -12,7 +12,6 @@
     <sheet name="Evidence Citations" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Reperformance" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Evidence Inventory" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Decision Log" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -21,10 +20,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.0000"/>
-  </numFmts>
-  <fonts count="17">
+  <numFmts count="0"/>
+  <fonts count="16">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -119,10 +116,6 @@
       <i val="1"/>
       <color rgb="00A17321"/>
       <sz val="10"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="000B362C"/>
     </font>
   </fonts>
   <fills count="5">
@@ -218,7 +211,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -256,11 +249,6 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -693,7 +681,7 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>03 Jul 2026, 03:08 UTC</t>
+          <t>03 Jul 2026, 03:35 UTC</t>
         </is>
       </c>
     </row>
@@ -817,7 +805,7 @@
       </c>
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>Provide additional evidence to close “Inappropriate or excessive access identified during the review is remediated in a timely manner”. Specifically: The reviewer flagged one account (Danielle Goodwin) for revocation and the summary records remediation via ITSM ticket ITSM-48217 assigned to IT with a 5-business-day SLA.</t>
+          <t>Provide additional evidence to close “Inappropriate or excessive access identified during the review is remediated in a timely manner”. Specifically: The reviewer documented one exception (Danielle Goodwin) and evidenced a remediation action — ITSM-48217 was raised and assigned to IT with a 5-business-day SLA.</t>
         </is>
       </c>
     </row>
@@ -976,11 +964,11 @@
         </is>
       </c>
       <c r="C2" s="17" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="D2" s="17" t="inlineStr">
         <is>
-          <t>The evidence file uar-netsuite-q2-2026.xlsx documents a Q2 2026 Periodic (Quarterly) User Access Review for NetSuite (Production), completed on 2026-06-30 (within Q2 2026). All 334 rows on the Access Review sheet share a single review date of 2026-06-30, and the Cover sheet explicitly identifies the cadence ("Periodic (Quarterly) User Access Review") and completion date. This attribute concerns cadence and completion timing only; substantive issues (e.g., missed terminated user) are scoped to other attributes. Only limitation is that a single quarter's evidence is provided, so full-period cadence adherence across all quarters cannot be independently confirmed from this sample alone.</t>
+          <t>The evidence shows a Q2 2026 quarterly access review for NetSuite (Production) was performed and completed on 2026-06-30, with a documented review date on every reviewed row and a Cover sheet declaring the review type as "Periodic (Quarterly) User Access Review". This directly evidences that a review occurred in the audit period, at the defined quarterly cadence, with the review date documented. The interval between consecutive reviews cannot be fully assessed from a single quarter's file, but the cadence declaration and dated Q2 2026 completion satisfy the criteria for this sample.</t>
         </is>
       </c>
       <c r="E2" s="17" t="n">
@@ -988,7 +976,7 @@
       </c>
       <c r="F2" s="17" t="inlineStr">
         <is>
-          <t>Only one quarter (Q2 2026) of evidence was provided in this sample; verdict is on the observed cycle. If the audit period spans multiple quarters, additional quarters' UAR packs would be needed to fully confirm no skipped cycles.</t>
+          <t>Interval-between-consecutive-reviews criterion: only Q2 2026 is in evidence; no prior quarter's UAR file was provided, so interval cannot be directly measured. Accepted as satisfied for this sample based on the documented quarterly cadence declaration, but would require prior-period UAR to fully verify.</t>
         </is>
       </c>
     </row>
@@ -1008,16 +996,15 @@
       </c>
       <c r="D3" s="17" t="inlineStr">
         <is>
-          <t>The Cover sheet identifies Priya Nadkarni, Director, Finance Systems as the System Owner and Reviewer/Approver for NetSuite (Production), and the Access Review sheet consistently lists her as "Reviewed By" for all sampled rows on 2026-06-30. An electronic sign-off attestation is documented ("Approved electronically by Priya Nadkarni on 2026-06-30"). Priya is not present in the reviewed user population (she does not appear as a user in the NetSuite export), so she did not review her own access. The population reviewed (334 rows) reconciles to the system export (334 rows). Note: this attribute concerns reviewer appropriateness/independence/sign-off — the separate reconciliation finding (Kevin Lewis missed) belongs to a different attribute and is not held against this one.</t>
+          <t>The reviewer is identified by name and role on the Cover sheet as "Priya Nadkarni, Director, Finance Systems (System Owner)" and is the sole "Reviewed By" name across all 332 in-scope Access Review rows. Reviewer sign-off is documented ("Approved electronically by Priya Nadkarni on 2026-06-30"). IPE checks reconcile the 334-row export to 332 in-scope + 2 service accounts, and reviewer decisions (331 retain / 1 revoke) tie to Cover totals, evidencing that the approval covers the complete in-scope population.</t>
         </is>
       </c>
       <c r="E3" s="17" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F3" s="17" t="inlineStr">
         <is>
-          <t>Considered whether the reviewer might also be a user of the system (self-review) — she is not present in the system access export.
-Considered whether reconciliation gaps (Kevin Lewis missed, service account orphans) undermine this attribute — they pertain to review completeness/effectiveness, a separate attribute, and do not affect reviewer appropriateness/independence/sign-off.</t>
+          <t>Service-account carve-out (2 orphan accounts marked 'n/a - out of scope') was considered; this does not undermine population completeness because the carve-out is explicit and reconciles to IPE checks.</t>
         </is>
       </c>
     </row>
@@ -1037,7 +1024,7 @@
       </c>
       <c r="D4" s="17" t="inlineStr">
         <is>
-          <t>The reviewer flagged one account (Danielle Goodwin) for revocation and the summary records remediation via ITSM ticket ITSM-48217 assigned to IT with a 5-business-day SLA. However, no evidence has been provided showing (a) the ticket itself, (b) that the access was actually revoked, or (c) post-remediation confirmation that the account is now inactive in NetSuite. Additionally, the reperformance identified a second terminated-but-active account (Kevin Lewis) that the reviewer incorrectly retained — this is a reviewer-completeness issue, not strictly a remediation-timeliness issue, but it means only 1 of 2 real findings entered the remediation workflow. To reach SUCCESS, provide the ITSM-48217 ticket record with closure date and a post-remediation NetSuite screenshot showing Danielle Goodwin's account is inactive/deleted.</t>
+          <t>The reviewer documented one exception (Danielle Goodwin) and evidenced a remediation action — ITSM-48217 was raised and assigned to IT with a 5-business-day SLA. However, the workbook only shows the ticket was raised; there is no evidence that the access was actually revoked in NetSuite (e.g., closed ticket, deprovisioning confirmation, or updated system export showing status=Inactive). Additionally, the reperformer independently identified a second exception (Kevin Lewis — terminated in HRIS but reviewer decided "retain"), which the reviewer missed entirely and therefore no remediation was undertaken; however that gap belongs to the "completeness of exception identification" attribute rather than "timeliness of remediation of identified exceptions." To flip this to SUCCESS, evidence is needed that ITSM-48217 was closed and Danielle Goodwin's NetSuite account is now Inactive, along with the closure date to assess timeliness against the 5-business-day SLA.</t>
         </is>
       </c>
       <c r="E4" s="17" t="n">
@@ -1045,8 +1032,8 @@
       </c>
       <c r="F4" s="17" t="inlineStr">
         <is>
-          <t>Considered whether Kevin Lewis being missed by the reviewer belongs to a separate 'reviewer completeness' attribute rather than this timeliness attribute — it primarily does, but it is noted because remediation cannot be timely for a finding that was never raised.
-Considered whether the narrative statement 'remediated via ITSM-48217' on the Cover sheet is sufficient evidence — rejected because there is no independent artefact (ticket export or post-remediation system screenshot) confirming the revocation actually occurred.</t>
+          <t>Considered whether the ticket number ITSM-48217 alone constitutes sufficient evidence of remediation. Rejected — a ticket being raised evidences a remediation request, not that access was actually revoked in the target system. The attribute explicitly requires 'evidence confirms the access was actually revoked or adjusted in the target system (not just requested).'
+Considered whether Kevin Lewis (missed by reviewer) should cause this attribute to FAIL. Rejected — Kevin Lewis was not 'identified during the review' by the reviewer, so remediation timeliness for identified exceptions is not directly impugned. That gap belongs to the exception-identification attribute.</t>
         </is>
       </c>
     </row>
@@ -1061,7 +1048,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -1105,12 +1092,12 @@
       </c>
       <c r="C2" s="17" t="inlineStr">
         <is>
-          <t>Cover!Review Period / Review Type / Review Completed</t>
+          <t>Cover!Review Type / Review Period / Review Completed</t>
         </is>
       </c>
       <c r="D2" s="17" t="inlineStr">
         <is>
-          <t>Cover metadata states Review Period = 'Q2 2026', Review Type = 'Periodic (Quarterly) User Access Review', Review Completed = '2026-06-30', with Reviewer Sign-off 'Approved electronically by Priya Nadkarni on 2026-06-30.'</t>
+          <t>Cover sheet declares Review Period 'Q2 2026', Review Type 'Periodic (Quarterly) User Access Review', and Review Completed '2026-06-30'.</t>
         </is>
       </c>
     </row>
@@ -1127,12 +1114,12 @@
       </c>
       <c r="C3" s="17" t="inlineStr">
         <is>
-          <t>Access Review!H2:H335 (Review Date column)</t>
+          <t>Access Review!H2:H6 (Review Date column)</t>
         </is>
       </c>
       <c r="D3" s="17" t="inlineStr">
         <is>
-          <t>All 334 reviewer rows carry Review Date = 2026-06-30, evidencing a completed review within Q2 2026.</t>
+          <t>All sampled Access Review rows show Review Date 2026-06-30; deterministic reperformance found a single unique review date (2026-06-30) across all 334 rows.</t>
         </is>
       </c>
     </row>
@@ -1149,12 +1136,12 @@
       </c>
       <c r="C4" s="17" t="inlineStr">
         <is>
-          <t>Deterministic reperformance: unique_review_dates</t>
+          <t>Cover!Reviewer Sign-off</t>
         </is>
       </c>
       <c r="D4" s="17" t="inlineStr">
         <is>
-          <t>Reperformance confirms exactly one unique review date (2026-06-30) across the population, consistent with a single quarterly cycle.</t>
+          <t>'Approved electronically by Priya Nadkarni on 2026-06-30' — confirms review completion date is documented and signed off.</t>
         </is>
       </c>
     </row>
@@ -1176,7 +1163,7 @@
       </c>
       <c r="D5" s="17" t="inlineStr">
         <is>
-          <t>Reviewer / Approver identified as 'Priya Nadkarni, Director, Finance Systems (System Owner)' for NetSuite (Production).</t>
+          <t>Reviewer/Approver identified as 'Priya Nadkarni, Director, Finance Systems (System Owner)'.</t>
         </is>
       </c>
     </row>
@@ -1198,7 +1185,7 @@
       </c>
       <c r="D6" s="17" t="inlineStr">
         <is>
-          <t>'Approved electronically by Priya Nadkarni on 2026-06-30.' — documented sign-off.</t>
+          <t>Sign-off recorded: 'Approved electronically by Priya Nadkarni on 2026-06-30.'</t>
         </is>
       </c>
     </row>
@@ -1215,12 +1202,12 @@
       </c>
       <c r="C7" s="17" t="inlineStr">
         <is>
-          <t>Access Review!G2:G6 (Reviewed By column, sampled rows)</t>
+          <t>Access Review!G2:G335 (Reviewed By column)</t>
         </is>
       </c>
       <c r="D7" s="17" t="inlineStr">
         <is>
-          <t>All sampled rows show 'Priya Nadkarni' as Reviewed By with Review Date 2026-06-30.</t>
+          <t>All 334 rows show 'Priya Nadkarni' as Reviewed By with Review Date 2026-06-30 (single reviewer, single date).</t>
         </is>
       </c>
     </row>
@@ -1237,19 +1224,19 @@
       </c>
       <c r="C8" s="17" t="inlineStr">
         <is>
-          <t>System Access Export (full user list)</t>
+          <t>IPE checks / Cover totals</t>
         </is>
       </c>
       <c r="D8" s="17" t="inlineStr">
         <is>
-          <t>Priya Nadkarni does not appear as a user in the NetSuite access export — she did not review her own access.</t>
+          <t>Reperformance confirms 332 in-scope accounts fully covered (331 retain + 1 revoke reconciles to Cover); 2 service accounts appropriately scoped out.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="17" t="inlineStr">
         <is>
-          <t>Access is reviewed and approved by an appropriate system or data owner</t>
+          <t>Inappropriate or excessive access identified during the review is remediated in a timely manner</t>
         </is>
       </c>
       <c r="B9" s="17" t="inlineStr">
@@ -1259,12 +1246,12 @@
       </c>
       <c r="C9" s="17" t="inlineStr">
         <is>
-          <t>Deterministic reperformance: reviewer_names, unique_review_dates</t>
+          <t>Cover!Observation 1</t>
         </is>
       </c>
       <c r="D9" s="17" t="inlineStr">
         <is>
-          <t>Single reviewer 'Priya Nadkarni' and single review date '2026-06-30' across all 334 rows; reviewer_sheet_rows (334) equals system_export_rows (334).</t>
+          <t>States Danielle Goodwin retains ACTIVE access despite HRIS termination 2021-12-03; remediation: access flagged for immediate revocation; deprovisioning ticket ITSM-48217 raised, assigned to IT Identity &amp; Access, due within 5 business days.</t>
         </is>
       </c>
     </row>
@@ -1281,12 +1268,12 @@
       </c>
       <c r="C10" s="17" t="inlineStr">
         <is>
-          <t>Cover!Observation 1</t>
+          <t>Access Review!E90 (Danielle Goodwin row)</t>
         </is>
       </c>
       <c r="D10" s="17" t="inlineStr">
         <is>
-          <t>States Danielle Goodwin retains ACTIVE access despite HRIS termination effective 2021-12-03; access flagged for immediate revocation and deprovisioning ticket ITSM-48217 raised, assigned to IT Identity &amp; Access, due within 5 business days.</t>
+          <t>Reviewer Decision = 'revoke' — the exception is documented on the reviewer sheet.</t>
         </is>
       </c>
     </row>
@@ -1303,12 +1290,12 @@
       </c>
       <c r="C11" s="17" t="inlineStr">
         <is>
-          <t>Cover!Conclusion</t>
+          <t>System Access Export!C90</t>
         </is>
       </c>
       <c r="D11" s="17" t="inlineStr">
         <is>
-          <t>'Review complete. 1 observation raised and remediated via ITSM-48217.' — narrative claims remediation but no supporting ticket artefact provided.</t>
+          <t>Danielle Goodwin account still shows Account Status = Active in the export dated 26 Jun 2026 — no post-remediation export provided to confirm the access was actually revoked.</t>
         </is>
       </c>
     </row>
@@ -1325,12 +1312,12 @@
       </c>
       <c r="C12" s="17" t="inlineStr">
         <is>
-          <t>Access Review!E90 (Danielle Goodwin row)</t>
+          <t>Cover!Conclusion</t>
         </is>
       </c>
       <c r="D12" s="17" t="inlineStr">
         <is>
-          <t>Reviewer Decision = 'revoke' for danielle.goodwin@northpeakfinancial.com — the flagged item is documented with a remediation action in the review workbook.</t>
+          <t>States '1 observation raised and remediated via ITSM-48217' but provides no ticket closure date or confirmation of actual deprovisioning in NetSuite.</t>
         </is>
       </c>
     </row>
@@ -1342,39 +1329,17 @@
       </c>
       <c r="B13" s="17" t="inlineStr">
         <is>
-          <t>uar-netsuite-q2-2026.xlsx</t>
+          <t>reperformance (deterministic)</t>
         </is>
       </c>
       <c r="C13" s="17" t="inlineStr">
         <is>
-          <t>Access Review!E187 (Kevin Lewis row)</t>
+          <t>reviewer_missed_findings</t>
         </is>
       </c>
       <c r="D13" s="17" t="inlineStr">
         <is>
-          <t>Reviewer Decision = 'retain' for kevin.lewis@northpeakfinancial.com despite HRIS showing terminated — this account was not flagged for remediation, so no remediation was triggered.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="17" t="inlineStr">
-        <is>
-          <t>Inappropriate or excessive access identified during the review is remediated in a timely manner</t>
-        </is>
-      </c>
-      <c r="B14" s="17" t="inlineStr">
-        <is>
-          <t>deterministic reperformance</t>
-        </is>
-      </c>
-      <c r="C14" s="17" t="inlineStr">
-        <is>
-          <t>reviewer_missed_findings / terminated_but_active_in_system</t>
-        </is>
-      </c>
-      <c r="D14" s="17" t="inlineStr">
-        <is>
-          <t>Reperformance identifies 2 terminated-but-active accounts (Danielle Goodwin, Kevin Lewis); only Danielle Goodwin entered the remediation workflow.</t>
+          <t>Reperformer identified Kevin Lewis (terminated in HRIS, still active in system) — reviewer decision was 'retain' so no remediation initiated. Not an in-scope failure for this attribute (belongs to identification-completeness), but noted.</t>
         </is>
       </c>
     </row>
@@ -1517,212 +1482,8 @@
       </c>
       <c r="E3" s="17" t="inlineStr">
         <is>
-          <t>periodic-review-cadence, periodic-review-cadence, periodic-review-cadence, reviewer-is-appropriate-owner, reviewer-is-appropriate-owner, reviewer-is-appropriate-owner, reviewer-is-appropriate-owner, reviewer-is-appropriate-owner, timely-remediation-of-exceptions, timely-remediation-of-exceptions, timely-remediation-of-exceptions, timely-remediation-of-exceptions</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:I5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="55" customWidth="1" min="3" max="3"/>
-    <col width="24" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="16" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B1" s="16" t="inlineStr">
-        <is>
-          <t>Timestamp</t>
-        </is>
-      </c>
-      <c r="C1" s="16" t="inlineStr">
-        <is>
-          <t>Purpose</t>
-        </is>
-      </c>
-      <c r="D1" s="16" t="inlineStr">
-        <is>
-          <t>Model</t>
-        </is>
-      </c>
-      <c r="E1" s="16" t="inlineStr">
-        <is>
-          <t>Input tokens</t>
-        </is>
-      </c>
-      <c r="F1" s="16" t="inlineStr">
-        <is>
-          <t>Cache read</t>
-        </is>
-      </c>
-      <c r="G1" s="16" t="inlineStr">
-        <is>
-          <t>Output tokens</t>
-        </is>
-      </c>
-      <c r="H1" s="16" t="inlineStr">
-        <is>
-          <t>Cost USD</t>
-        </is>
-      </c>
-      <c r="I1" s="16" t="inlineStr">
-        <is>
-          <t>Latency (ms)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" s="17" t="inlineStr">
-        <is>
-          <t>2026-07-03T03:07:26.779685Z</t>
-        </is>
-      </c>
-      <c r="C2" s="17" t="inlineStr">
-        <is>
-          <t>judge:periodic-review-cadence:sample-1</t>
-        </is>
-      </c>
-      <c r="D2" s="17" t="inlineStr">
-        <is>
-          <t>claude-opus-4-7</t>
-        </is>
-      </c>
-      <c r="E2" s="17" t="n">
-        <v>26340</v>
-      </c>
-      <c r="F2" s="17" t="n">
-        <v>2638</v>
-      </c>
-      <c r="G2" s="17" t="n">
-        <v>954</v>
-      </c>
-      <c r="H2" s="23" t="n">
-        <v>0.431037</v>
-      </c>
-      <c r="I2" s="17" t="n">
-        <v>14399</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" s="17" t="inlineStr">
-        <is>
-          <t>2026-07-03T03:07:42.695100Z</t>
-        </is>
-      </c>
-      <c r="C3" s="17" t="inlineStr">
-        <is>
-          <t>judge:reviewer-is-appropriate-owner:sample-1</t>
-        </is>
-      </c>
-      <c r="D3" s="17" t="inlineStr">
-        <is>
-          <t>claude-opus-4-7</t>
-        </is>
-      </c>
-      <c r="E3" s="17" t="n">
-        <v>26363</v>
-      </c>
-      <c r="F3" s="17" t="n">
-        <v>2638</v>
-      </c>
-      <c r="G3" s="17" t="n">
-        <v>1177</v>
-      </c>
-      <c r="H3" s="23" t="n">
-        <v>0.448107</v>
-      </c>
-      <c r="I3" s="17" t="n">
-        <v>15910</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" s="17" t="inlineStr">
-        <is>
-          <t>2026-07-03T03:08:00.049737Z</t>
-        </is>
-      </c>
-      <c r="C4" s="17" t="inlineStr">
-        <is>
-          <t>judge:timely-remediation-of-exceptions:sample-1</t>
-        </is>
-      </c>
-      <c r="D4" s="17" t="inlineStr">
-        <is>
-          <t>claude-opus-4-7</t>
-        </is>
-      </c>
-      <c r="E4" s="17" t="n">
-        <v>26361</v>
-      </c>
-      <c r="F4" s="17" t="n">
-        <v>2638</v>
-      </c>
-      <c r="G4" s="17" t="n">
-        <v>1326</v>
-      </c>
-      <c r="H4" s="23" t="n">
-        <v>0.459252</v>
-      </c>
-      <c r="I4" s="17" t="n">
-        <v>17344</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="C5" s="24" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="E5" s="24">
-        <f>SUM(E2:E4)</f>
-        <v/>
-      </c>
-      <c r="F5" s="24">
-        <f>SUM(F2:F4)</f>
-        <v/>
-      </c>
-      <c r="G5" s="24">
-        <f>SUM(G2:G4)</f>
-        <v/>
-      </c>
-      <c r="H5" s="25">
-        <f>SUM(H2:H4)</f>
-        <v/>
-      </c>
-      <c r="I5" s="24">
-        <f>SUM(I2:I4)</f>
-        <v/>
+          <t>periodic-access-reviews, periodic-access-reviews, periodic-access-reviews, reviewed-approved-by-owner, reviewed-approved-by-owner, reviewed-approved-by-owner, reviewed-approved-by-owner, timely-remediation, timely-remediation, timely-remediation, timely-remediation</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/output/user-access-review/claude/sample-1/workpaper.xlsx
+++ b/output/user-access-review/claude/sample-1/workpaper.xlsx
@@ -12,6 +12,7 @@
     <sheet name="Evidence Citations" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Reperformance" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Evidence Inventory" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Decision Log" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,8 +21,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="16">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.0000"/>
+  </numFmts>
+  <fonts count="17">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -117,6 +120,10 @@
       <color rgb="00A17321"/>
       <sz val="10"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="000B362C"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -211,7 +218,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -249,6 +256,11 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -681,7 +693,7 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>03 Jul 2026, 03:35 UTC</t>
+          <t>03 Jul 2026, 03:38 UTC</t>
         </is>
       </c>
     </row>
@@ -805,7 +817,7 @@
       </c>
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>Provide additional evidence to close “Inappropriate or excessive access identified during the review is remediated in a timely manner”. Specifically: The reviewer documented one exception (Danielle Goodwin) and evidenced a remediation action — ITSM-48217 was raised and assigned to IT with a 5-business-day SLA.</t>
+          <t>Provide additional evidence to close “Inappropriate or excessive access identified during the review is remediated in a timely manner”. Specifically: The reviewer flagged one account (Danielle Goodwin) for revocation and a deprovisioning ticket ITSM-48217 was raised and assigned to IT with a 5-business-day SLA, but no evidence of actual ticket closure/completion or a system screenshot confirming the account was deprovisioned has been provided.</t>
         </is>
       </c>
     </row>
@@ -964,19 +976,19 @@
         </is>
       </c>
       <c r="C2" s="17" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="D2" s="17" t="inlineStr">
         <is>
-          <t>The evidence shows a Q2 2026 quarterly access review for NetSuite (Production) was performed and completed on 2026-06-30, with a documented review date on every reviewed row and a Cover sheet declaring the review type as "Periodic (Quarterly) User Access Review". This directly evidences that a review occurred in the audit period, at the defined quarterly cadence, with the review date documented. The interval between consecutive reviews cannot be fully assessed from a single quarter's file, but the cadence declaration and dated Q2 2026 completion satisfy the criteria for this sample.</t>
+          <t>Evidence shows a Q2 2026 quarterly UAR was performed for NetSuite Production, completed on 2026-06-30 by Priya Nadkarni. The review covered all 334 users from the system access export (332 in-scope humans + 2 service accounts flagged out of scope), matching the population as of the review date. IPE checks reconcile system export row counts to the Cover sheet and reviewer decisions. Frequency labelled quarterly and completion date is documented; no prior-quarter review date is in evidence but the review type and completion are clearly stated.</t>
         </is>
       </c>
       <c r="E2" s="17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F2" s="17" t="inlineStr">
         <is>
-          <t>Interval-between-consecutive-reviews criterion: only Q2 2026 is in evidence; no prior quarter's UAR file was provided, so interval cannot be directly measured. Accepted as satisfied for this sample based on the documented quarterly cadence declaration, but would require prior-period UAR to fully verify.</t>
+          <t>Prior-quarter review date not directly evidenced; however the review is explicitly designated as Quarterly and completed 2026-06-30, satisfying the periodicity criterion for the period under review.</t>
         </is>
       </c>
     </row>
@@ -996,15 +1008,15 @@
       </c>
       <c r="D3" s="17" t="inlineStr">
         <is>
-          <t>The reviewer is identified by name and role on the Cover sheet as "Priya Nadkarni, Director, Finance Systems (System Owner)" and is the sole "Reviewed By" name across all 332 in-scope Access Review rows. Reviewer sign-off is documented ("Approved electronically by Priya Nadkarni on 2026-06-30"). IPE checks reconcile the 334-row export to 332 in-scope + 2 service accounts, and reviewer decisions (331 retain / 1 revoke) tie to Cover totals, evidencing that the approval covers the complete in-scope population.</t>
+          <t>The reviewer is identified on the Cover sheet as "Priya Nadkarni, Director, Finance Systems (System Owner)" — name and role are documented, and she is designated as the NetSuite system owner. All 334 rows on the Access Review sheet show "Reviewed By: Priya Nadkarni" with a review date, and the Cover sheet records electronic sign-off on 2026-06-30. Independence is satisfied: the reviewer's name does not appear as an in-scope user being reviewed (she is not among the listed NetSuite user accounts), and the workbook was prepared by a separate individual (Marcus Bell). Documented approval is captured via the signed workbook and per-line reviewer attribution.</t>
         </is>
       </c>
       <c r="E3" s="17" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F3" s="17" t="inlineStr">
         <is>
-          <t>Service-account carve-out (2 orphan accounts marked 'n/a - out of scope') was considered; this does not undermine population completeness because the carve-out is explicit and reconciles to IPE checks.</t>
+          <t>Considered whether reviewer independence is compromised by self-review; Priya Nadkarni is not in the in-scope user list, so she did not self-approve.</t>
         </is>
       </c>
     </row>
@@ -1024,16 +1036,15 @@
       </c>
       <c r="D4" s="17" t="inlineStr">
         <is>
-          <t>The reviewer documented one exception (Danielle Goodwin) and evidenced a remediation action — ITSM-48217 was raised and assigned to IT with a 5-business-day SLA. However, the workbook only shows the ticket was raised; there is no evidence that the access was actually revoked in NetSuite (e.g., closed ticket, deprovisioning confirmation, or updated system export showing status=Inactive). Additionally, the reperformer independently identified a second exception (Kevin Lewis — terminated in HRIS but reviewer decided "retain"), which the reviewer missed entirely and therefore no remediation was undertaken; however that gap belongs to the "completeness of exception identification" attribute rather than "timeliness of remediation of identified exceptions." To flip this to SUCCESS, evidence is needed that ITSM-48217 was closed and Danielle Goodwin's NetSuite account is now Inactive, along with the closure date to assess timeliness against the 5-business-day SLA.</t>
+          <t>The reviewer flagged one account (Danielle Goodwin) for revocation and a deprovisioning ticket ITSM-48217 was raised and assigned to IT with a 5-business-day SLA, but no evidence of actual ticket closure/completion or a system screenshot confirming the account was deprovisioned has been provided. Additionally, the reperformance identified a second terminated-but-active account (Kevin Lewis) that the reviewer incorrectly marked "retain" — this is a completeness issue for identifying flagged items, but for THIS attribute (timeliness of remediation of items that were flagged), we can only assess the one item that was flagged. To flip to SUCCESS, provide evidence that ITSM-48217 was closed (deprovisioning log, ticket resolution timestamp, or NetSuite screenshot showing the account inactive) within the SLA window following the 2026-06-30 review completion.</t>
         </is>
       </c>
       <c r="E4" s="17" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F4" s="17" t="inlineStr">
         <is>
-          <t>Considered whether the ticket number ITSM-48217 alone constitutes sufficient evidence of remediation. Rejected — a ticket being raised evidences a remediation request, not that access was actually revoked in the target system. The attribute explicitly requires 'evidence confirms the access was actually revoked or adjusted in the target system (not just requested).'
-Considered whether Kevin Lewis (missed by reviewer) should cause this attribute to FAIL. Rejected — Kevin Lewis was not 'identified during the review' by the reviewer, so remediation timeliness for identified exceptions is not directly impugned. That gap belongs to the exception-identification attribute.</t>
+          <t>Kevin Lewis (terminated but active, reviewer marked 'retain') was NOT flagged by the reviewer, so it does not fall within this attribute's scope (timeliness of remediation of flagged items) — it is a reviewer-completeness issue belonging to a different attribute. Noted but not used as a basis for this verdict.</t>
         </is>
       </c>
     </row>
@@ -1048,7 +1059,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -1092,12 +1103,12 @@
       </c>
       <c r="C2" s="17" t="inlineStr">
         <is>
-          <t>Cover!Review Type / Review Period / Review Completed</t>
+          <t>Cover!Review Period / Review Type / Review Completed</t>
         </is>
       </c>
       <c r="D2" s="17" t="inlineStr">
         <is>
-          <t>Cover sheet declares Review Period 'Q2 2026', Review Type 'Periodic (Quarterly) User Access Review', and Review Completed '2026-06-30'.</t>
+          <t>Review Period = Q2 2026; Review Type = Periodic (Quarterly) User Access Review; Review Completed = 2026-06-30; Reviewer/Approver = Priya Nadkarni.</t>
         </is>
       </c>
     </row>
@@ -1114,12 +1125,12 @@
       </c>
       <c r="C3" s="17" t="inlineStr">
         <is>
-          <t>Access Review!H2:H6 (Review Date column)</t>
+          <t>Access Review sheet (334 rows) Review Date column</t>
         </is>
       </c>
       <c r="D3" s="17" t="inlineStr">
         <is>
-          <t>All sampled Access Review rows show Review Date 2026-06-30; deterministic reperformance found a single unique review date (2026-06-30) across all 334 rows.</t>
+          <t>All rows carry Review Date 2026-06-30, reviewed by Priya Nadkarni.</t>
         </is>
       </c>
     </row>
@@ -1136,34 +1147,34 @@
       </c>
       <c r="C4" s="17" t="inlineStr">
         <is>
-          <t>Cover!Reviewer Sign-off</t>
+          <t>System Access Export sheet (334 rows)</t>
         </is>
       </c>
       <c r="D4" s="17" t="inlineStr">
         <is>
-          <t>'Approved electronically by Priya Nadkarni on 2026-06-30' — confirms review completion date is documented and signed off.</t>
+          <t>Population of 334 accounts covered by the Access Review sheet (332 in-scope + 2 service accounts marked out of scope).</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="17" t="inlineStr">
         <is>
-          <t>Access is reviewed and approved by an appropriate system or data owner</t>
+          <t>Access reviews are performed on a periodic basis (e.g. quarterly)</t>
         </is>
       </c>
       <c r="B5" s="17" t="inlineStr">
         <is>
-          <t>uar-netsuite-q2-2026.xlsx</t>
+          <t>deterministic reperformance</t>
         </is>
       </c>
       <c r="C5" s="17" t="inlineStr">
         <is>
-          <t>Cover!Reviewer / Approver</t>
+          <t>ipe_checks</t>
         </is>
       </c>
       <c r="D5" s="17" t="inlineStr">
         <is>
-          <t>Reviewer/Approver identified as 'Priya Nadkarni, Director, Finance Systems (System Owner)'.</t>
+          <t>All three IPE checks pass: export row count reconciles to Cover, service-account carve-out matches, and reviewer decision counts (331 retain / 1 revoke) tie to Cover.</t>
         </is>
       </c>
     </row>
@@ -1180,12 +1191,12 @@
       </c>
       <c r="C6" s="17" t="inlineStr">
         <is>
-          <t>Cover!Reviewer Sign-off</t>
+          <t>Cover!Reviewer / Approver</t>
         </is>
       </c>
       <c r="D6" s="17" t="inlineStr">
         <is>
-          <t>Sign-off recorded: 'Approved electronically by Priya Nadkarni on 2026-06-30.'</t>
+          <t>Reviewer / Approver identified as 'Priya Nadkarni, Director, Finance Systems (System Owner)'.</t>
         </is>
       </c>
     </row>
@@ -1202,12 +1213,12 @@
       </c>
       <c r="C7" s="17" t="inlineStr">
         <is>
-          <t>Access Review!G2:G335 (Reviewed By column)</t>
+          <t>Cover!Reviewer Sign-off</t>
         </is>
       </c>
       <c r="D7" s="17" t="inlineStr">
         <is>
-          <t>All 334 rows show 'Priya Nadkarni' as Reviewed By with Review Date 2026-06-30 (single reviewer, single date).</t>
+          <t>'Approved electronically by Priya Nadkarni on 2026-06-30.'</t>
         </is>
       </c>
     </row>
@@ -1224,19 +1235,19 @@
       </c>
       <c r="C8" s="17" t="inlineStr">
         <is>
-          <t>IPE checks / Cover totals</t>
+          <t>Access Review!G2:G335 (Reviewed By column)</t>
         </is>
       </c>
       <c r="D8" s="17" t="inlineStr">
         <is>
-          <t>Reperformance confirms 332 in-scope accounts fully covered (331 retain + 1 revoke reconciles to Cover); 2 service accounts appropriately scoped out.</t>
+          <t>All 334 rows attributed to 'Priya Nadkarni' with Review Date 2026-06-30; reperformance confirms only one unique reviewer name.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="17" t="inlineStr">
         <is>
-          <t>Inappropriate or excessive access identified during the review is remediated in a timely manner</t>
+          <t>Access is reviewed and approved by an appropriate system or data owner</t>
         </is>
       </c>
       <c r="B9" s="17" t="inlineStr">
@@ -1246,19 +1257,19 @@
       </c>
       <c r="C9" s="17" t="inlineStr">
         <is>
-          <t>Cover!Observation 1</t>
+          <t>Cover!Prepared By</t>
         </is>
       </c>
       <c r="D9" s="17" t="inlineStr">
         <is>
-          <t>States Danielle Goodwin retains ACTIVE access despite HRIS termination 2021-12-03; remediation: access flagged for immediate revocation; deprovisioning ticket ITSM-48217 raised, assigned to IT Identity &amp; Access, due within 5 business days.</t>
+          <t>Prepared by Marcus Bell, IT Compliance Analyst — separate individual from reviewer.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="17" t="inlineStr">
         <is>
-          <t>Inappropriate or excessive access identified during the review is remediated in a timely manner</t>
+          <t>Access is reviewed and approved by an appropriate system or data owner</t>
         </is>
       </c>
       <c r="B10" s="17" t="inlineStr">
@@ -1268,12 +1279,12 @@
       </c>
       <c r="C10" s="17" t="inlineStr">
         <is>
-          <t>Access Review!E90 (Danielle Goodwin row)</t>
+          <t>System Access Export (Username list)</t>
         </is>
       </c>
       <c r="D10" s="17" t="inlineStr">
         <is>
-          <t>Reviewer Decision = 'revoke' — the exception is documented on the reviewer sheet.</t>
+          <t>Priya Nadkarni does not appear in the list of in-scope NetSuite user accounts being reviewed — reviewer is not reviewing her own access.</t>
         </is>
       </c>
     </row>
@@ -1290,12 +1301,12 @@
       </c>
       <c r="C11" s="17" t="inlineStr">
         <is>
-          <t>System Access Export!C90</t>
+          <t>Cover!Observation 1</t>
         </is>
       </c>
       <c r="D11" s="17" t="inlineStr">
         <is>
-          <t>Danielle Goodwin account still shows Account Status = Active in the export dated 26 Jun 2026 — no post-remediation export provided to confirm the access was actually revoked.</t>
+          <t>States Danielle Goodwin's access was flagged for immediate revocation and deprovisioning ticket ITSM-48217 was raised and assigned to IT Identity &amp; Access with due date within 5 business days. No evidence of ticket closure or actual deprovisioning provided.</t>
         </is>
       </c>
     </row>
@@ -1312,12 +1323,12 @@
       </c>
       <c r="C12" s="17" t="inlineStr">
         <is>
-          <t>Cover!Conclusion</t>
+          <t>Cover!Review Completed / Reviewer Sign-off</t>
         </is>
       </c>
       <c r="D12" s="17" t="inlineStr">
         <is>
-          <t>States '1 observation raised and remediated via ITSM-48217' but provides no ticket closure date or confirmation of actual deprovisioning in NetSuite.</t>
+          <t>Review completed 2026-06-30; conclusion states '1 observation raised and remediated via ITSM-48217' but no supporting ticket closure artefact is included in the workbook.</t>
         </is>
       </c>
     </row>
@@ -1329,17 +1340,39 @@
       </c>
       <c r="B13" s="17" t="inlineStr">
         <is>
-          <t>reperformance (deterministic)</t>
+          <t>uar-netsuite-q2-2026.xlsx</t>
         </is>
       </c>
       <c r="C13" s="17" t="inlineStr">
         <is>
-          <t>reviewer_missed_findings</t>
+          <t>Access Review!E90 (Danielle Goodwin row)</t>
         </is>
       </c>
       <c r="D13" s="17" t="inlineStr">
         <is>
-          <t>Reperformer identified Kevin Lewis (terminated in HRIS, still active in system) — reviewer decision was 'retain' so no remediation initiated. Not an in-scope failure for this attribute (belongs to identification-completeness), but noted.</t>
+          <t>Reviewer decision recorded as 'revoke' — this is the sole flagged item requiring remediation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="17" t="inlineStr">
+        <is>
+          <t>Inappropriate or excessive access identified during the review is remediated in a timely manner</t>
+        </is>
+      </c>
+      <c r="B14" s="17" t="inlineStr">
+        <is>
+          <t>reperformance</t>
+        </is>
+      </c>
+      <c r="C14" s="17" t="inlineStr">
+        <is>
+          <t>terminated_but_active_in_system / system_status for danielle.goodwin</t>
+        </is>
+      </c>
+      <c r="D14" s="17" t="inlineStr">
+        <is>
+          <t>As of the reperformance snapshot, Danielle Goodwin's system_status is still 'active' in the NetSuite export, indicating the revocation may not yet have been executed at the point the export was taken.</t>
         </is>
       </c>
     </row>
@@ -1482,8 +1515,212 @@
       </c>
       <c r="E3" s="17" t="inlineStr">
         <is>
-          <t>periodic-access-reviews, periodic-access-reviews, periodic-access-reviews, reviewed-approved-by-owner, reviewed-approved-by-owner, reviewed-approved-by-owner, reviewed-approved-by-owner, timely-remediation, timely-remediation, timely-remediation, timely-remediation</t>
-        </is>
+          <t>periodic-access-reviews, periodic-access-reviews, periodic-access-reviews, reviewed-approved-by-owner, reviewed-approved-by-owner, reviewed-approved-by-owner, reviewed-approved-by-owner, reviewed-approved-by-owner, timely-remediation, timely-remediation, timely-remediation</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="55" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="16" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B1" s="16" t="inlineStr">
+        <is>
+          <t>Timestamp</t>
+        </is>
+      </c>
+      <c r="C1" s="16" t="inlineStr">
+        <is>
+          <t>Purpose</t>
+        </is>
+      </c>
+      <c r="D1" s="16" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="E1" s="16" t="inlineStr">
+        <is>
+          <t>Input tokens</t>
+        </is>
+      </c>
+      <c r="F1" s="16" t="inlineStr">
+        <is>
+          <t>Cache read</t>
+        </is>
+      </c>
+      <c r="G1" s="16" t="inlineStr">
+        <is>
+          <t>Output tokens</t>
+        </is>
+      </c>
+      <c r="H1" s="16" t="inlineStr">
+        <is>
+          <t>Cost USD</t>
+        </is>
+      </c>
+      <c r="I1" s="16" t="inlineStr">
+        <is>
+          <t>Latency (ms)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-03T03:37:02.684171Z</t>
+        </is>
+      </c>
+      <c r="C2" s="17" t="inlineStr">
+        <is>
+          <t>judge:periodic-access-reviews:sample-1</t>
+        </is>
+      </c>
+      <c r="D2" s="17" t="inlineStr">
+        <is>
+          <t>claude-opus-4-7</t>
+        </is>
+      </c>
+      <c r="E2" s="17" t="n">
+        <v>79848</v>
+      </c>
+      <c r="F2" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" s="17" t="n">
+        <v>3215</v>
+      </c>
+      <c r="H2" s="23" t="n">
+        <v>1.438845</v>
+      </c>
+      <c r="I2" s="17" t="n">
+        <v>16819</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-03T03:37:58.077439Z</t>
+        </is>
+      </c>
+      <c r="C3" s="17" t="inlineStr">
+        <is>
+          <t>judge:reviewed-approved-by-owner:sample-1</t>
+        </is>
+      </c>
+      <c r="D3" s="17" t="inlineStr">
+        <is>
+          <t>claude-opus-4-7</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="n">
+        <v>79923</v>
+      </c>
+      <c r="F3" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" s="17" t="n">
+        <v>3083</v>
+      </c>
+      <c r="H3" s="23" t="n">
+        <v>1.43007</v>
+      </c>
+      <c r="I3" s="17" t="n">
+        <v>15865</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="17" t="inlineStr">
+        <is>
+          <t>2026-07-03T03:38:45.335967Z</t>
+        </is>
+      </c>
+      <c r="C4" s="17" t="inlineStr">
+        <is>
+          <t>judge:timely-remediation:sample-1</t>
+        </is>
+      </c>
+      <c r="D4" s="17" t="inlineStr">
+        <is>
+          <t>claude-opus-4-7</t>
+        </is>
+      </c>
+      <c r="E4" s="17" t="n">
+        <v>79917</v>
+      </c>
+      <c r="F4" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="17" t="n">
+        <v>3488</v>
+      </c>
+      <c r="H4" s="23" t="n">
+        <v>1.460355</v>
+      </c>
+      <c r="I4" s="17" t="n">
+        <v>15866</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="C5" s="24" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="E5" s="24">
+        <f>SUM(E2:E4)</f>
+        <v/>
+      </c>
+      <c r="F5" s="24">
+        <f>SUM(F2:F4)</f>
+        <v/>
+      </c>
+      <c r="G5" s="24">
+        <f>SUM(G2:G4)</f>
+        <v/>
+      </c>
+      <c r="H5" s="25">
+        <f>SUM(H2:H4)</f>
+        <v/>
+      </c>
+      <c r="I5" s="24">
+        <f>SUM(I2:I4)</f>
+        <v/>
       </c>
     </row>
   </sheetData>

--- a/output/user-access-review/claude/sample-1/workpaper.xlsx
+++ b/output/user-access-review/claude/sample-1/workpaper.xlsx
@@ -24,7 +24,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.0000"/>
   </numFmts>
-  <fonts count="17">
+  <fonts count="16">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -53,7 +53,7 @@
     <font>
       <name val="SF Pro Text"/>
       <b val="1"/>
-      <color rgb="00A17321"/>
+      <color rgb="00B83A2E"/>
       <sz val="16"/>
     </font>
     <font>
@@ -76,13 +76,13 @@
     <font>
       <name val="SF Pro Text"/>
       <b val="1"/>
-      <color rgb="00A17321"/>
+      <color rgb="00B83A2E"/>
       <sz val="9"/>
     </font>
     <font>
       <name val="SF Pro Text"/>
       <b val="1"/>
-      <color rgb="00B83A2E"/>
+      <color rgb="00A17321"/>
       <sz val="9"/>
     </font>
     <font>
@@ -105,7 +105,7 @@
     <font>
       <name val="SF Pro Text"/>
       <b val="1"/>
-      <color rgb="00A17321"/>
+      <color rgb="00B83A2E"/>
       <sz val="10"/>
     </font>
     <font>
@@ -113,12 +113,6 @@
       <b val="1"/>
       <color rgb="00148F72"/>
       <sz val="12"/>
-    </font>
-    <font>
-      <name val="SF Pro Text"/>
-      <i val="1"/>
-      <color rgb="00A17321"/>
-      <sz val="10"/>
     </font>
     <font>
       <b val="1"/>
@@ -134,7 +128,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F5EDD9"/>
+        <fgColor rgb="00F4E1DF"/>
       </patternFill>
     </fill>
     <fill>
@@ -218,7 +212,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -253,14 +247,11 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -626,7 +617,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D31"/>
+  <dimension ref="A1:D30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -657,7 +648,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>CONTROL INCONCLUSIVE</t>
+          <t>CONTROL FAIL</t>
         </is>
       </c>
     </row>
@@ -693,7 +684,7 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>03 Jul 2026, 03:38 UTC</t>
+          <t>03 Jul 2026, 04:02 UTC</t>
         </is>
       </c>
     </row>
@@ -707,7 +698,7 @@
     <row r="11" ht="60" customHeight="1">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>The control cannot be signed off from this evidence bundle. 1 attribute(s) need further evidence, 2 passed, and none positively failed. Request the missing evidence and re-audit. Deterministic reperformance surfaced 1 finding(s) the reviewer missed — see the reperformance summary.</t>
+          <t>The control failed. 1 of 3 attribute(s) were positively contradicted by the evidence. The auditee has open remediation to complete before this control can be signed off. Deterministic reperformance surfaced 1 finding(s) the reviewer missed — see the reperformance summary.</t>
         </is>
       </c>
     </row>
@@ -721,12 +712,12 @@
     <row r="14">
       <c r="A14" s="9" t="inlineStr">
         <is>
-          <t>WARN</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>Insufficient evidence: Inappropriate or excessive access identified during the review is remediated in a timely manner</t>
+          <t>Inappropriate or excessive access identified during the review is remediated in a timely manner</t>
         </is>
       </c>
     </row>
@@ -755,7 +746,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="10" t="inlineStr">
+      <c r="A17" s="9" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -767,7 +758,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="9" t="inlineStr">
+      <c r="A18" s="10" t="inlineStr">
         <is>
           <t>WARN</t>
         </is>
@@ -779,7 +770,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="9" t="inlineStr">
+      <c r="A19" s="10" t="inlineStr">
         <is>
           <t>WARN</t>
         </is>
@@ -790,60 +781,58 @@
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="9" t="inlineStr">
-        <is>
-          <t>WARN</t>
-        </is>
-      </c>
-      <c r="B20" s="8" t="inlineStr">
-        <is>
-          <t>Evidence file(s) were provided but not cited by any verdict: hris-employee-export.xlsx. Confirm relevance or extraction gap.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="7" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr">
         <is>
           <t>Recommended actions</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="30" customHeight="1">
+      <c r="A22" s="11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B22" s="8" t="inlineStr">
+        <is>
+          <t>Remediate the root cause of the FAIL on “Inappropriate or excessive access identified during the review is remediated in a timely manner”, then re-submit for testing. Rationale: Deterministic reperformance identified a terminated employee, Kevin Lewis (HRIS status: terminated), whose NetSuite account remains Active and whom the reviewer marked "Retain" — inappropriate access exists that was neither flagged nor remediated.</t>
         </is>
       </c>
     </row>
     <row r="23" ht="30" customHeight="1">
       <c r="A23" s="11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>Provide additional evidence to close “Inappropriate or excessive access identified during the review is remediated in a timely manner”. Specifically: The reviewer flagged one account (Danielle Goodwin) for revocation and a deprovisioning ticket ITSM-48217 was raised and assigned to IT with a 5-business-day SLA, but no evidence of actual ticket closure/completion or a system screenshot confirming the account was deprovisioned has been provided.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="30" customHeight="1">
-      <c r="A24" s="11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B24" s="8" t="inlineStr">
-        <is>
           <t>Revoke Kevin Lewis's access (kevin.lewis@northpeakfinancial.com) and update the review process to catch terminated employees still marked Retain.</t>
         </is>
       </c>
     </row>
+    <row r="25">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t>Reviewer sign-off</t>
+        </is>
+      </c>
+    </row>
     <row r="26">
-      <c r="A26" s="7" t="inlineStr">
-        <is>
-          <t>Reviewer sign-off</t>
-        </is>
-      </c>
+      <c r="A26" s="12" t="inlineStr">
+        <is>
+          <t>Decision (Accept / Rework / Reject)</t>
+        </is>
+      </c>
+      <c r="B26" s="13" t="inlineStr"/>
+      <c r="C26" s="14" t="n"/>
+      <c r="D26" s="15" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="12" t="inlineStr">
         <is>
-          <t>Decision (Accept / Rework / Reject)</t>
+          <t>Reviewer name</t>
         </is>
       </c>
       <c r="B27" s="13" t="inlineStr"/>
@@ -853,7 +842,7 @@
     <row r="28">
       <c r="A28" s="12" t="inlineStr">
         <is>
-          <t>Reviewer name</t>
+          <t>Reviewer role</t>
         </is>
       </c>
       <c r="B28" s="13" t="inlineStr"/>
@@ -863,7 +852,7 @@
     <row r="29">
       <c r="A29" s="12" t="inlineStr">
         <is>
-          <t>Reviewer role</t>
+          <t>Date</t>
         </is>
       </c>
       <c r="B29" s="13" t="inlineStr"/>
@@ -873,43 +862,32 @@
     <row r="30">
       <c r="A30" s="12" t="inlineStr">
         <is>
-          <t>Date</t>
+          <t>Comments</t>
         </is>
       </c>
       <c r="B30" s="13" t="inlineStr"/>
       <c r="C30" s="14" t="n"/>
       <c r="D30" s="15" t="n"/>
     </row>
-    <row r="31">
-      <c r="A31" s="12" t="inlineStr">
-        <is>
-          <t>Comments</t>
-        </is>
-      </c>
-      <c r="B31" s="13" t="inlineStr"/>
-      <c r="C31" s="14" t="n"/>
-      <c r="D31" s="15" t="n"/>
-    </row>
   </sheetData>
-  <mergeCells count="18">
+  <mergeCells count="17">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="B28:D28"/>
     <mergeCell ref="B19:D19"/>
     <mergeCell ref="B14:D14"/>
     <mergeCell ref="B29:D29"/>
-    <mergeCell ref="B31:D31"/>
     <mergeCell ref="B23:D23"/>
+    <mergeCell ref="B22:D22"/>
     <mergeCell ref="B4:D4"/>
     <mergeCell ref="B17:D17"/>
     <mergeCell ref="B18:D18"/>
+    <mergeCell ref="B26:D26"/>
     <mergeCell ref="B27:D27"/>
     <mergeCell ref="B30:D30"/>
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="A11:D11"/>
     <mergeCell ref="B15:D15"/>
-    <mergeCell ref="B24:D24"/>
     <mergeCell ref="B16:D16"/>
-    <mergeCell ref="B20:D20"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -976,21 +954,17 @@
         </is>
       </c>
       <c r="C2" s="17" t="n">
-        <v>0.9</v>
+        <v>0.92</v>
       </c>
       <c r="D2" s="17" t="inlineStr">
         <is>
-          <t>Evidence shows a Q2 2026 quarterly UAR was performed for NetSuite Production, completed on 2026-06-30 by Priya Nadkarni. The review covered all 334 users from the system access export (332 in-scope humans + 2 service accounts flagged out of scope), matching the population as of the review date. IPE checks reconcile system export row counts to the Cover sheet and reviewer decisions. Frequency labelled quarterly and completion date is documented; no prior-quarter review date is in evidence but the review type and completion are clearly stated.</t>
+          <t>The Cover sheet positively identifies the Review Type as "Periodic (Quarterly) User Access Review" for Review Period Q2 2026, with Review Completed 2026-06-30. All 334 reviewer decision rows on the Access Review sheet carry a single Review Date of 2026-06-30, consistent with a single quarterly cycle, and IPE checks reconcile the population (334 accounts; 332 in-scope + 2 service) to the Cover totals. The review covered the in-scope NetSuite Production user population as of the review date.</t>
         </is>
       </c>
       <c r="E2" s="17" t="n">
         <v>4</v>
       </c>
-      <c r="F2" s="17" t="inlineStr">
-        <is>
-          <t>Prior-quarter review date not directly evidenced; however the review is explicitly designated as Quarterly and completed 2026-06-30, satisfying the periodicity criterion for the period under review.</t>
-        </is>
-      </c>
+      <c r="F2" s="17" t="inlineStr"/>
     </row>
     <row r="3" ht="80" customHeight="1">
       <c r="A3" s="17" t="inlineStr">
@@ -1008,17 +982,13 @@
       </c>
       <c r="D3" s="17" t="inlineStr">
         <is>
-          <t>The reviewer is identified on the Cover sheet as "Priya Nadkarni, Director, Finance Systems (System Owner)" — name and role are documented, and she is designated as the NetSuite system owner. All 334 rows on the Access Review sheet show "Reviewed By: Priya Nadkarni" with a review date, and the Cover sheet records electronic sign-off on 2026-06-30. Independence is satisfied: the reviewer's name does not appear as an in-scope user being reviewed (she is not among the listed NetSuite user accounts), and the workbook was prepared by a separate individual (Marcus Bell). Documented approval is captured via the signed workbook and per-line reviewer attribution.</t>
+          <t>The reviewer is named as Priya Nadkarni, Director, Finance Systems (System Owner) on the Cover sheet, an appropriate owner role for NetSuite (Production). She is distinct from the preparer (Marcus Bell) and is not on the reviewed access list (she is not among the 334 usernames), so she is independent of the users reviewed. Sign-off is documented ("Approved electronically by Priya Nadkarni on 2026-06-30") and dated the same day as the Review Completed date, satisfying the documented, on-or-after approval criterion.</t>
         </is>
       </c>
       <c r="E3" s="17" t="n">
-        <v>5</v>
-      </c>
-      <c r="F3" s="17" t="inlineStr">
-        <is>
-          <t>Considered whether reviewer independence is compromised by self-review; Priya Nadkarni is not in the in-scope user list, so she did not self-approve.</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="F3" s="17" t="inlineStr"/>
     </row>
     <row r="4" ht="80" customHeight="1">
       <c r="A4" s="17" t="inlineStr">
@@ -1028,23 +998,24 @@
       </c>
       <c r="B4" s="19" t="inlineStr">
         <is>
-          <t>FURTHER_EVIDENCE_REQUIRED</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="C4" s="17" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="D4" s="17" t="inlineStr">
         <is>
-          <t>The reviewer flagged one account (Danielle Goodwin) for revocation and a deprovisioning ticket ITSM-48217 was raised and assigned to IT with a 5-business-day SLA, but no evidence of actual ticket closure/completion or a system screenshot confirming the account was deprovisioned has been provided. Additionally, the reperformance identified a second terminated-but-active account (Kevin Lewis) that the reviewer incorrectly marked "retain" — this is a completeness issue for identifying flagged items, but for THIS attribute (timeliness of remediation of items that were flagged), we can only assess the one item that was flagged. To flip to SUCCESS, provide evidence that ITSM-48217 was closed (deprovisioning log, ticket resolution timestamp, or NetSuite screenshot showing the account inactive) within the SLA window following the 2026-06-30 review completion.</t>
+          <t>Deterministic reperformance identified a terminated employee, Kevin Lewis (HRIS status: terminated), whose NetSuite account remains Active and whom the reviewer marked "Retain" — inappropriate access exists that was neither flagged nor remediated. While the one item the reviewer did flag (Danielle Goodwin) has a documented remediation path via ITSM-48217, the reperformance surfaces at least one additional case of inappropriate access that was missed and left in place, contradicting the criterion that all flagged inappropriate access be remediated. Evidence of actual system removal (deprovisioning confirmation for Danielle Goodwin) is also not present — only a ticket reference.</t>
         </is>
       </c>
       <c r="E4" s="17" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F4" s="17" t="inlineStr">
         <is>
-          <t>Kevin Lewis (terminated but active, reviewer marked 'retain') was NOT flagged by the reviewer, so it does not fall within this attribute's scope (timeliness of remediation of flagged items) — it is a reviewer-completeness issue belonging to a different attribute. Noted but not used as a basis for this verdict.</t>
+          <t>Considered whether the two service accounts (svc-bank-recon, svc-netsuite-integration) constitute inappropriate access — Cover sheet explicitly scopes them out as integration accounts, so they are not an exception issue for this attribute.
+Considered whether Danielle Goodwin's ticketed remediation alone satisfies the criterion — rejected because the reperformance surfaces an additional un-remediated case (Kevin Lewis) and no evidence confirms actual system removal for Danielle Goodwin.</t>
         </is>
       </c>
     </row>
@@ -1103,12 +1074,12 @@
       </c>
       <c r="C2" s="17" t="inlineStr">
         <is>
-          <t>Cover!Review Period / Review Type / Review Completed</t>
+          <t>Cover!Review Type / Review Period / Review Completed</t>
         </is>
       </c>
       <c r="D2" s="17" t="inlineStr">
         <is>
-          <t>Review Period = Q2 2026; Review Type = Periodic (Quarterly) User Access Review; Review Completed = 2026-06-30; Reviewer/Approver = Priya Nadkarni.</t>
+          <t>Cover sheet declares Review Type: 'Periodic (Quarterly) User Access Review', Review Period: 'Q2 2026', Review Completed: '2026-06-30', System: 'NetSuite (Production)', Scope: 'All human user accounts with access to NetSuite Production.'</t>
         </is>
       </c>
     </row>
@@ -1125,12 +1096,12 @@
       </c>
       <c r="C3" s="17" t="inlineStr">
         <is>
-          <t>Access Review sheet (334 rows) Review Date column</t>
+          <t>Access Review!H2:H335 (Review Date column)</t>
         </is>
       </c>
       <c r="D3" s="17" t="inlineStr">
         <is>
-          <t>All rows carry Review Date 2026-06-30, reviewed by Priya Nadkarni.</t>
+          <t>unique_review_dates = ['2026-06-30']; every one of the 334 reviewer decision rows is dated 2026-06-30, indicating a single quarterly review cycle.</t>
         </is>
       </c>
     </row>
@@ -1147,12 +1118,12 @@
       </c>
       <c r="C4" s="17" t="inlineStr">
         <is>
-          <t>System Access Export sheet (334 rows)</t>
+          <t>Cover!Reviewer Sign-off</t>
         </is>
       </c>
       <c r="D4" s="17" t="inlineStr">
         <is>
-          <t>Population of 334 accounts covered by the Access Review sheet (332 in-scope + 2 service accounts marked out of scope).</t>
+          <t>'Approved electronically by Priya Nadkarni on 2026-06-30.' — completion date documented and signed.</t>
         </is>
       </c>
     </row>
@@ -1164,17 +1135,17 @@
       </c>
       <c r="B5" s="17" t="inlineStr">
         <is>
-          <t>deterministic reperformance</t>
+          <t>uar-netsuite-q2-2026.xlsx</t>
         </is>
       </c>
       <c r="C5" s="17" t="inlineStr">
         <is>
-          <t>ipe_checks</t>
+          <t>IPE checks (reperformance)</t>
         </is>
       </c>
       <c r="D5" s="17" t="inlineStr">
         <is>
-          <t>All three IPE checks pass: export row count reconciles to Cover, service-account carve-out matches, and reviewer decision counts (331 retain / 1 revoke) tie to Cover.</t>
+          <t>IPE reconciliation passes: 334 export rows = 332 in-scope + 2 service accounts, matching Cover totals; population as of review date is fully covered.</t>
         </is>
       </c>
     </row>
@@ -1213,12 +1184,12 @@
       </c>
       <c r="C7" s="17" t="inlineStr">
         <is>
-          <t>Cover!Reviewer Sign-off</t>
+          <t>Cover!Reviewer Sign-off and Review Completed</t>
         </is>
       </c>
       <c r="D7" s="17" t="inlineStr">
         <is>
-          <t>'Approved electronically by Priya Nadkarni on 2026-06-30.'</t>
+          <t>'Approved electronically by Priya Nadkarni on 2026-06-30.' with Review Completed 2026-06-30.</t>
         </is>
       </c>
     </row>
@@ -1240,7 +1211,7 @@
       </c>
       <c r="D8" s="17" t="inlineStr">
         <is>
-          <t>All 334 rows attributed to 'Priya Nadkarni' with Review Date 2026-06-30; reperformance confirms only one unique reviewer name.</t>
+          <t>All 334 rows show 'Priya Nadkarni' as the reviewer with Review Date 2026-06-30.</t>
         </is>
       </c>
     </row>
@@ -1257,19 +1228,19 @@
       </c>
       <c r="C9" s="17" t="inlineStr">
         <is>
-          <t>Cover!Prepared By</t>
+          <t>Cover!Prepared By vs Reviewer</t>
         </is>
       </c>
       <c r="D9" s="17" t="inlineStr">
         <is>
-          <t>Prepared by Marcus Bell, IT Compliance Analyst — separate individual from reviewer.</t>
+          <t>Preparer (Marcus Bell) is distinct from Reviewer (Priya Nadkarni); Priya Nadkarni does not appear in the list of 334 in-scope usernames, confirming she is not reviewing her own access.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="17" t="inlineStr">
         <is>
-          <t>Access is reviewed and approved by an appropriate system or data owner</t>
+          <t>Inappropriate or excessive access identified during the review is remediated in a timely manner</t>
         </is>
       </c>
       <c r="B10" s="17" t="inlineStr">
@@ -1279,12 +1250,12 @@
       </c>
       <c r="C10" s="17" t="inlineStr">
         <is>
-          <t>System Access Export (Username list)</t>
+          <t>Access Review!E187 (Kevin Lewis row)</t>
         </is>
       </c>
       <c r="D10" s="17" t="inlineStr">
         <is>
-          <t>Priya Nadkarni does not appear in the list of in-scope NetSuite user accounts being reviewed — reviewer is not reviewing her own access.</t>
+          <t>Reviewer Decision = 'Retain' for kevin.lewis@northpeakfinancial.com despite HRIS showing him terminated.</t>
         </is>
       </c>
     </row>
@@ -1296,17 +1267,17 @@
       </c>
       <c r="B11" s="17" t="inlineStr">
         <is>
-          <t>uar-netsuite-q2-2026.xlsx</t>
+          <t>hris-employee-export.xlsx</t>
         </is>
       </c>
       <c r="C11" s="17" t="inlineStr">
         <is>
-          <t>Cover!Observation 1</t>
+          <t>Employees!D127 (Kevin Lewis)</t>
         </is>
       </c>
       <c r="D11" s="17" t="inlineStr">
         <is>
-          <t>States Danielle Goodwin's access was flagged for immediate revocation and deprovisioning ticket ITSM-48217 was raised and assigned to IT Identity &amp; Access with due date within 5 business days. No evidence of ticket closure or actual deprovisioning provided.</t>
+          <t>HRIS record for Kevin Lewis shows employment status terminated, contradicting the retained decision.</t>
         </is>
       </c>
     </row>
@@ -1323,12 +1294,12 @@
       </c>
       <c r="C12" s="17" t="inlineStr">
         <is>
-          <t>Cover!Review Completed / Reviewer Sign-off</t>
+          <t>Cover sheet — Observation 1 / Conclusion</t>
         </is>
       </c>
       <c r="D12" s="17" t="inlineStr">
         <is>
-          <t>Review completed 2026-06-30; conclusion states '1 observation raised and remediated via ITSM-48217' but no supporting ticket closure artefact is included in the workbook.</t>
+          <t>Only 1 observation raised (Danielle Goodwin) with remediation via ITSM-48217; no mention of Kevin Lewis or any other terminated-but-active user.</t>
         </is>
       </c>
     </row>
@@ -1340,17 +1311,17 @@
       </c>
       <c r="B13" s="17" t="inlineStr">
         <is>
-          <t>uar-netsuite-q2-2026.xlsx</t>
+          <t>reperformance</t>
         </is>
       </c>
       <c r="C13" s="17" t="inlineStr">
         <is>
-          <t>Access Review!E90 (Danielle Goodwin row)</t>
+          <t>reviewer_missed_findings (count=1)</t>
         </is>
       </c>
       <c r="D13" s="17" t="inlineStr">
         <is>
-          <t>Reviewer decision recorded as 'revoke' — this is the sole flagged item requiring remediation.</t>
+          <t>Reconciliation flagged Kevin Lewis as terminated-in-HRIS but retained by the reviewer — a case of inappropriate access not identified and not remediated.</t>
         </is>
       </c>
     </row>
@@ -1362,17 +1333,17 @@
       </c>
       <c r="B14" s="17" t="inlineStr">
         <is>
-          <t>reperformance</t>
+          <t>uar-netsuite-q2-2026.xlsx</t>
         </is>
       </c>
       <c r="C14" s="17" t="inlineStr">
         <is>
-          <t>terminated_but_active_in_system / system_status for danielle.goodwin</t>
+          <t>Cover sheet — Observation 1 remediation text</t>
         </is>
       </c>
       <c r="D14" s="17" t="inlineStr">
         <is>
-          <t>As of the reperformance snapshot, Danielle Goodwin's system_status is still 'active' in the NetSuite export, indicating the revocation may not yet have been executed at the point the export was taken.</t>
+          <t>Remediation for Danielle Goodwin is only a raised ticket (ITSM-48217, due within 5 business days); no evidence provided that the account was actually deprovisioned in NetSuite.</t>
         </is>
       </c>
     </row>
@@ -1488,9 +1459,9 @@
           <t>Workbook · 2 sheet(s), 720 rows total. Sheets: Employees, Notes</t>
         </is>
       </c>
-      <c r="E2" s="22" t="inlineStr">
-        <is>
-          <t>— uncited —</t>
+      <c r="E2" s="17" t="inlineStr">
+        <is>
+          <t>timely-remediation</t>
         </is>
       </c>
     </row>
@@ -1515,7 +1486,7 @@
       </c>
       <c r="E3" s="17" t="inlineStr">
         <is>
-          <t>periodic-access-reviews, periodic-access-reviews, periodic-access-reviews, reviewed-approved-by-owner, reviewed-approved-by-owner, reviewed-approved-by-owner, reviewed-approved-by-owner, reviewed-approved-by-owner, timely-remediation, timely-remediation, timely-remediation</t>
+          <t>periodic-review-cadence, periodic-review-cadence, periodic-review-cadence, periodic-review-cadence, reviewed-approved-by-owner, reviewed-approved-by-owner, reviewed-approved-by-owner, reviewed-approved-by-owner, timely-remediation, timely-remediation, timely-remediation</t>
         </is>
       </c>
     </row>
@@ -1597,12 +1568,12 @@
       </c>
       <c r="B2" s="17" t="inlineStr">
         <is>
-          <t>2026-07-03T03:37:02.684171Z</t>
+          <t>2026-07-03T04:02:28.582885Z</t>
         </is>
       </c>
       <c r="C2" s="17" t="inlineStr">
         <is>
-          <t>judge:periodic-access-reviews:sample-1</t>
+          <t>judge:periodic-review-cadence:sample-1</t>
         </is>
       </c>
       <c r="D2" s="17" t="inlineStr">
@@ -1611,19 +1582,19 @@
         </is>
       </c>
       <c r="E2" s="17" t="n">
-        <v>79848</v>
+        <v>26600</v>
       </c>
       <c r="F2" s="17" t="n">
         <v>0</v>
       </c>
       <c r="G2" s="17" t="n">
-        <v>3215</v>
-      </c>
-      <c r="H2" s="23" t="n">
-        <v>1.438845</v>
+        <v>940</v>
+      </c>
+      <c r="H2" s="22" t="n">
+        <v>0.48891375</v>
       </c>
       <c r="I2" s="17" t="n">
-        <v>16819</v>
+        <v>12379</v>
       </c>
     </row>
     <row r="3">
@@ -1632,7 +1603,7 @@
       </c>
       <c r="B3" s="17" t="inlineStr">
         <is>
-          <t>2026-07-03T03:37:58.077439Z</t>
+          <t>2026-07-03T04:02:39.916718Z</t>
         </is>
       </c>
       <c r="C3" s="17" t="inlineStr">
@@ -1646,19 +1617,19 @@
         </is>
       </c>
       <c r="E3" s="17" t="n">
-        <v>79923</v>
+        <v>26647</v>
       </c>
       <c r="F3" s="17" t="n">
-        <v>0</v>
+        <v>5177</v>
       </c>
       <c r="G3" s="17" t="n">
-        <v>3083</v>
-      </c>
-      <c r="H3" s="23" t="n">
-        <v>1.43007</v>
+        <v>904</v>
+      </c>
+      <c r="H3" s="22" t="n">
+        <v>0.3976155</v>
       </c>
       <c r="I3" s="17" t="n">
-        <v>15865</v>
+        <v>11331</v>
       </c>
     </row>
     <row r="4">
@@ -1667,7 +1638,7 @@
       </c>
       <c r="B4" s="17" t="inlineStr">
         <is>
-          <t>2026-07-03T03:38:45.335967Z</t>
+          <t>2026-07-03T04:02:58.039390Z</t>
         </is>
       </c>
       <c r="C4" s="17" t="inlineStr">
@@ -1681,44 +1652,44 @@
         </is>
       </c>
       <c r="E4" s="17" t="n">
-        <v>79917</v>
+        <v>26650</v>
       </c>
       <c r="F4" s="17" t="n">
-        <v>0</v>
+        <v>5177</v>
       </c>
       <c r="G4" s="17" t="n">
-        <v>3488</v>
-      </c>
-      <c r="H4" s="23" t="n">
-        <v>1.460355</v>
+        <v>1208</v>
+      </c>
+      <c r="H4" s="22" t="n">
+        <v>0.4204605</v>
       </c>
       <c r="I4" s="17" t="n">
-        <v>15866</v>
+        <v>18118</v>
       </c>
     </row>
     <row r="5">
-      <c r="C5" s="24" t="inlineStr">
+      <c r="C5" s="23" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="E5" s="24">
+      <c r="E5" s="23">
         <f>SUM(E2:E4)</f>
         <v/>
       </c>
-      <c r="F5" s="24">
+      <c r="F5" s="23">
         <f>SUM(F2:F4)</f>
         <v/>
       </c>
-      <c r="G5" s="24">
+      <c r="G5" s="23">
         <f>SUM(G2:G4)</f>
         <v/>
       </c>
-      <c r="H5" s="25">
+      <c r="H5" s="24">
         <f>SUM(H2:H4)</f>
         <v/>
       </c>
-      <c r="I5" s="24">
+      <c r="I5" s="23">
         <f>SUM(I2:I4)</f>
         <v/>
       </c>

--- a/output/user-access-review/claude/sample-1/workpaper.xlsx
+++ b/output/user-access-review/claude/sample-1/workpaper.xlsx
@@ -24,7 +24,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.0000"/>
   </numFmts>
-  <fonts count="16">
+  <fonts count="17">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -113,6 +113,12 @@
       <b val="1"/>
       <color rgb="00148F72"/>
       <sz val="12"/>
+    </font>
+    <font>
+      <name val="SF Pro Text"/>
+      <i val="1"/>
+      <color rgb="00A17321"/>
+      <sz val="10"/>
     </font>
     <font>
       <b val="1"/>
@@ -212,7 +218,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -247,11 +253,14 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -617,7 +626,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D30"/>
+  <dimension ref="A1:D31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -672,7 +681,7 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>claude:claude-opus-4-7</t>
+          <t>claude:claude-opus-4-8</t>
         </is>
       </c>
     </row>
@@ -684,7 +693,7 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>03 Jul 2026, 04:02 UTC</t>
+          <t>03 Jul 2026, 04:23 UTC</t>
         </is>
       </c>
     </row>
@@ -781,58 +790,60 @@
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="7" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="10" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="B20" s="8" t="inlineStr">
+        <is>
+          <t>Evidence file(s) were provided but not cited by any verdict: hris-employee-export.xlsx. Confirm relevance or extraction gap.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="inlineStr">
         <is>
           <t>Recommended actions</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="30" customHeight="1">
-      <c r="A22" s="11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B22" s="8" t="inlineStr">
-        <is>
-          <t>Remediate the root cause of the FAIL on “Inappropriate or excessive access identified during the review is remediated in a timely manner”, then re-submit for testing. Rationale: Deterministic reperformance identified a terminated employee, Kevin Lewis (HRIS status: terminated), whose NetSuite account remains Active and whom the reviewer marked "Retain" — inappropriate access exists that was neither flagged nor remediated.</t>
         </is>
       </c>
     </row>
     <row r="23" ht="30" customHeight="1">
       <c r="A23" s="11" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B23" s="8" t="inlineStr">
+        <is>
+          <t>Remediate the root cause of the FAIL on “Inappropriate or excessive access identified during the review is remediated in a timely manner”, then re-submit for testing. Rationale: The deterministic reperformance surfaced a second terminated-but-still-active user, Kevin Lewis (A/P Clerk, terminated in HRIS, system account still Active), whom the reviewer marked "retain" — a reviewer_missed finding.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="30" customHeight="1">
+      <c r="A24" s="11" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B23" s="8" t="inlineStr">
+      <c r="B24" s="8" t="inlineStr">
         <is>
           <t>Revoke Kevin Lewis's access (kevin.lewis@northpeakfinancial.com) and update the review process to catch terminated employees still marked Retain.</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="7" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="7" t="inlineStr">
         <is>
           <t>Reviewer sign-off</t>
         </is>
       </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="12" t="inlineStr">
-        <is>
-          <t>Decision (Accept / Rework / Reject)</t>
-        </is>
-      </c>
-      <c r="B26" s="13" t="inlineStr"/>
-      <c r="C26" s="14" t="n"/>
-      <c r="D26" s="15" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="12" t="inlineStr">
         <is>
-          <t>Reviewer name</t>
+          <t>Decision (Accept / Rework / Reject)</t>
         </is>
       </c>
       <c r="B27" s="13" t="inlineStr"/>
@@ -842,7 +853,7 @@
     <row r="28">
       <c r="A28" s="12" t="inlineStr">
         <is>
-          <t>Reviewer role</t>
+          <t>Reviewer name</t>
         </is>
       </c>
       <c r="B28" s="13" t="inlineStr"/>
@@ -852,7 +863,7 @@
     <row r="29">
       <c r="A29" s="12" t="inlineStr">
         <is>
-          <t>Date</t>
+          <t>Reviewer role</t>
         </is>
       </c>
       <c r="B29" s="13" t="inlineStr"/>
@@ -862,32 +873,43 @@
     <row r="30">
       <c r="A30" s="12" t="inlineStr">
         <is>
-          <t>Comments</t>
+          <t>Date</t>
         </is>
       </c>
       <c r="B30" s="13" t="inlineStr"/>
       <c r="C30" s="14" t="n"/>
       <c r="D30" s="15" t="n"/>
     </row>
+    <row r="31">
+      <c r="A31" s="12" t="inlineStr">
+        <is>
+          <t>Comments</t>
+        </is>
+      </c>
+      <c r="B31" s="13" t="inlineStr"/>
+      <c r="C31" s="14" t="n"/>
+      <c r="D31" s="15" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="17">
+  <mergeCells count="18">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="B28:D28"/>
     <mergeCell ref="B19:D19"/>
     <mergeCell ref="B14:D14"/>
     <mergeCell ref="B29:D29"/>
+    <mergeCell ref="B31:D31"/>
     <mergeCell ref="B23:D23"/>
-    <mergeCell ref="B22:D22"/>
     <mergeCell ref="B4:D4"/>
     <mergeCell ref="B17:D17"/>
     <mergeCell ref="B18:D18"/>
-    <mergeCell ref="B26:D26"/>
     <mergeCell ref="B27:D27"/>
     <mergeCell ref="B30:D30"/>
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="A11:D11"/>
     <mergeCell ref="B15:D15"/>
+    <mergeCell ref="B24:D24"/>
     <mergeCell ref="B16:D16"/>
+    <mergeCell ref="B20:D20"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -954,15 +976,15 @@
         </is>
       </c>
       <c r="C2" s="17" t="n">
-        <v>0.92</v>
+        <v>0.9</v>
       </c>
       <c r="D2" s="17" t="inlineStr">
         <is>
-          <t>The Cover sheet positively identifies the Review Type as "Periodic (Quarterly) User Access Review" for Review Period Q2 2026, with Review Completed 2026-06-30. All 334 reviewer decision rows on the Access Review sheet carry a single Review Date of 2026-06-30, consistent with a single quarterly cycle, and IPE checks reconcile the population (334 accounts; 332 in-scope + 2 service) to the Cover totals. The review covered the in-scope NetSuite Production user population as of the review date.</t>
+          <t>The Cover sheet declares the review as a "Periodic (Quarterly) User Access Review" for Review Period "Q2 2026", with "Review Completed: 2026-06-30" and an electronic sign-off dated 2026-06-30 — positively evidencing that a review was performed at the defined quarterly frequency with a documented date. All 334 reviewer decision rows carry a single Review Date of 2026-06-30, and the reperformance confirms exactly one unique review date, consistent with a single Q2 2026 cycle completed within the period. The reperformance findings about missed/inappropriate access relate to the review's accuracy, not its periodicity, so they do not bear on this attribute.</t>
         </is>
       </c>
       <c r="E2" s="17" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F2" s="17" t="inlineStr"/>
     </row>
@@ -978,17 +1000,22 @@
         </is>
       </c>
       <c r="C3" s="17" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="D3" s="17" t="inlineStr">
         <is>
-          <t>The reviewer is named as Priya Nadkarni, Director, Finance Systems (System Owner) on the Cover sheet, an appropriate owner role for NetSuite (Production). She is distinct from the preparer (Marcus Bell) and is not on the reviewed access list (she is not among the 334 usernames), so she is independent of the users reviewed. Sign-off is documented ("Approved electronically by Priya Nadkarni on 2026-06-30") and dated the same day as the Review Completed date, satisfying the documented, on-or-after approval criterion.</t>
+          <t>The Cover sheet identifies the reviewer/approver as Priya Nadkarni, Director, Finance Systems, explicitly designated "(System Owner)" for NetSuite Production, satisfying the identified-individual and appropriate-owner criteria. Documented approval exists via the sign-off line "Approved electronically by Priya Nadkarni on 2026-06-30," and all 334 review rows are attributed to Priya Nadkarni. Priya Nadkarni does not appear as a subject account in the NetSuite access export, so there is no self-approval concern. Note: reviewer-missed findings (e.g. Kevin Lewis) and remediation timeliness belong to separate attributes and do not bear on reviewer appropriateness/approval.</t>
         </is>
       </c>
       <c r="E3" s="17" t="n">
         <v>4</v>
       </c>
-      <c r="F3" s="17" t="inlineStr"/>
+      <c r="F3" s="17" t="inlineStr">
+        <is>
+          <t>Self-approval check: Priya Nadkarni is not among the reviewed subject accounts, so four-eyes/independence is not compromised for this attribute.
+Reviewer-missed findings and remediation timeliness (Kevin Lewis, Danielle Goodwin) were considered but excluded as they pertain to separate attributes (review completeness / remediation), not reviewer appropriateness.</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="80" customHeight="1">
       <c r="A4" s="17" t="inlineStr">
@@ -1002,20 +1029,20 @@
         </is>
       </c>
       <c r="C4" s="17" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="D4" s="17" t="inlineStr">
         <is>
-          <t>Deterministic reperformance identified a terminated employee, Kevin Lewis (HRIS status: terminated), whose NetSuite account remains Active and whom the reviewer marked "Retain" — inappropriate access exists that was neither flagged nor remediated. While the one item the reviewer did flag (Danielle Goodwin) has a documented remediation path via ITSM-48217, the reperformance surfaces at least one additional case of inappropriate access that was missed and left in place, contradicting the criterion that all flagged inappropriate access be remediated. Evidence of actual system removal (deprovisioning confirmation for Danielle Goodwin) is also not present — only a ticket reference.</t>
+          <t>The deterministic reperformance surfaced a second terminated-but-still-active user, Kevin Lewis (A/P Clerk, terminated in HRIS, system account still Active), whom the reviewer marked "retain" — a reviewer_missed finding. This is inappropriate access identified by the audit that was neither flagged nor remediated, contradicting the criterion. Separately, the one case the reviewer did catch (Danielle Goodwin) was flagged with ITSM-48217 due within 5 business days, but no completed remediation date is evidenced (the account was still Active at export). Because at least one instance of inappropriate access exists with no evidence of remediation, this attribute fails.</t>
         </is>
       </c>
       <c r="E4" s="17" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F4" s="17" t="inlineStr">
         <is>
-          <t>Considered whether the two service accounts (svc-bank-recon, svc-netsuite-integration) constitute inappropriate access — Cover sheet explicitly scopes them out as integration accounts, so they are not an exception issue for this attribute.
-Considered whether Danielle Goodwin's ticketed remediation alone satisfies the criterion — rejected because the reperformance surfaces an additional un-remediated case (Kevin Lewis) and no evidence confirms actual system removal for Danielle Goodwin.</t>
+          <t>Danielle Goodwin was flagged and a remediation ticket (ITSM-48217) raised, but this does not compensate for the missed Kevin Lewis case; and no evidence of a completed remediation date exists even for Danielle.
+On-leave-but-active users (8) treated as policy-dependent and not counted as clear inappropriate access; the terminated-but-active cases are the definitive finding.</t>
         </is>
       </c>
     </row>
@@ -1030,7 +1057,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -1074,12 +1101,12 @@
       </c>
       <c r="C2" s="17" t="inlineStr">
         <is>
-          <t>Cover!Review Type / Review Period / Review Completed</t>
+          <t>Cover sheet (Review Type / Review Period / Review Completed / Reviewer Sign-off)</t>
         </is>
       </c>
       <c r="D2" s="17" t="inlineStr">
         <is>
-          <t>Cover sheet declares Review Type: 'Periodic (Quarterly) User Access Review', Review Period: 'Q2 2026', Review Completed: '2026-06-30', System: 'NetSuite (Production)', Scope: 'All human user accounts with access to NetSuite Production.'</t>
+          <t>Review Type = 'Periodic (Quarterly) User Access Review'; Review Period = 'Q2 2026'; Review Completed = '2026-06-30'; Reviewer Sign-off = 'Approved electronically by Priya Nadkarni on 2026-06-30.'</t>
         </is>
       </c>
     </row>
@@ -1101,7 +1128,7 @@
       </c>
       <c r="D3" s="17" t="inlineStr">
         <is>
-          <t>unique_review_dates = ['2026-06-30']; every one of the 334 reviewer decision rows is dated 2026-06-30, indicating a single quarterly review cycle.</t>
+          <t>Every reviewer decision row is dated 2026-06-30, consistent with a single quarterly review cycle.</t>
         </is>
       </c>
     </row>
@@ -1113,24 +1140,24 @@
       </c>
       <c r="B4" s="17" t="inlineStr">
         <is>
-          <t>uar-netsuite-q2-2026.xlsx</t>
+          <t>reperformance (deterministic)</t>
         </is>
       </c>
       <c r="C4" s="17" t="inlineStr">
         <is>
-          <t>Cover!Reviewer Sign-off</t>
+          <t>unique_review_dates</t>
         </is>
       </c>
       <c r="D4" s="17" t="inlineStr">
         <is>
-          <t>'Approved electronically by Priya Nadkarni on 2026-06-30.' — completion date documented and signed.</t>
+          <t>Exactly one unique review date across all rows: 2026-06-30T00:00:00, confirming a single Q2 2026 cycle.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="17" t="inlineStr">
         <is>
-          <t>Access reviews are performed on a periodic basis (e.g. quarterly)</t>
+          <t>Access is reviewed and approved by an appropriate system or data owner</t>
         </is>
       </c>
       <c r="B5" s="17" t="inlineStr">
@@ -1140,12 +1167,12 @@
       </c>
       <c r="C5" s="17" t="inlineStr">
         <is>
-          <t>IPE checks (reperformance)</t>
+          <t>Cover!Reviewer / Approver</t>
         </is>
       </c>
       <c r="D5" s="17" t="inlineStr">
         <is>
-          <t>IPE reconciliation passes: 334 export rows = 332 in-scope + 2 service accounts, matching Cover totals; population as of review date is fully covered.</t>
+          <t>Reviewer/Approver identified as 'Priya Nadkarni, Director, Finance Systems (System Owner)' for NetSuite (Production).</t>
         </is>
       </c>
     </row>
@@ -1162,12 +1189,12 @@
       </c>
       <c r="C6" s="17" t="inlineStr">
         <is>
-          <t>Cover!Reviewer / Approver</t>
+          <t>Cover!Reviewer Sign-off</t>
         </is>
       </c>
       <c r="D6" s="17" t="inlineStr">
         <is>
-          <t>Reviewer / Approver identified as 'Priya Nadkarni, Director, Finance Systems (System Owner)'.</t>
+          <t>Documented approval: 'Approved electronically by Priya Nadkarni on 2026-06-30.'</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1211,12 @@
       </c>
       <c r="C7" s="17" t="inlineStr">
         <is>
-          <t>Cover!Reviewer Sign-off and Review Completed</t>
+          <t>Access Review!G2:G335 (Reviewed By)</t>
         </is>
       </c>
       <c r="D7" s="17" t="inlineStr">
         <is>
-          <t>'Approved electronically by Priya Nadkarni on 2026-06-30.' with Review Completed 2026-06-30.</t>
+          <t>All in-scope review rows attributed to reviewer Priya Nadkarni, dated 2026-06-30.</t>
         </is>
       </c>
     </row>
@@ -1201,39 +1228,39 @@
       </c>
       <c r="B8" s="17" t="inlineStr">
         <is>
-          <t>uar-netsuite-q2-2026.xlsx</t>
+          <t>reperformance</t>
         </is>
       </c>
       <c r="C8" s="17" t="inlineStr">
         <is>
-          <t>Access Review!G2:G335 (Reviewed By column)</t>
+          <t>reviewer_names / system_export subject list</t>
         </is>
       </c>
       <c r="D8" s="17" t="inlineStr">
         <is>
-          <t>All 334 rows show 'Priya Nadkarni' as the reviewer with Review Date 2026-06-30.</t>
+          <t>Sole reviewer is Priya Nadkarni; she does not appear as a subject account in the 334-row NetSuite access export, so no self-approval of her own access.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="17" t="inlineStr">
         <is>
-          <t>Access is reviewed and approved by an appropriate system or data owner</t>
+          <t>Inappropriate or excessive access identified during the review is remediated in a timely manner</t>
         </is>
       </c>
       <c r="B9" s="17" t="inlineStr">
         <is>
-          <t>uar-netsuite-q2-2026.xlsx</t>
+          <t>uar-netsuite-q2-2026.xlsx (reperformance)</t>
         </is>
       </c>
       <c r="C9" s="17" t="inlineStr">
         <is>
-          <t>Cover!Prepared By vs Reviewer</t>
+          <t>reviewer_missed_findings / terminated_but_active_in_system — kevin.lewis@northpeakfinancial.com</t>
         </is>
       </c>
       <c r="D9" s="17" t="inlineStr">
         <is>
-          <t>Preparer (Marcus Bell) is distinct from Reviewer (Priya Nadkarni); Priya Nadkarni does not appear in the list of 334 in-scope usernames, confirming she is not reviewing her own access.</t>
+          <t>Kevin Lewis is terminated in HRIS but his NetSuite account is still Active, and the reviewer decision is 'retain'. Access should have been revoked but was not identified or remediated.</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1277,12 @@
       </c>
       <c r="C10" s="17" t="inlineStr">
         <is>
-          <t>Access Review!E187 (Kevin Lewis row)</t>
+          <t>Access Review!E187 / System Access Export!C187 / HRIS Employees!D127</t>
         </is>
       </c>
       <c r="D10" s="17" t="inlineStr">
         <is>
-          <t>Reviewer Decision = 'Retain' for kevin.lewis@northpeakfinancial.com despite HRIS showing him terminated.</t>
+          <t>Kevin Lewis row: Account Status Active, reviewer decision Retain — no revocation, no remediation ticket, no remediation date.</t>
         </is>
       </c>
     </row>
@@ -1267,83 +1294,17 @@
       </c>
       <c r="B11" s="17" t="inlineStr">
         <is>
-          <t>hris-employee-export.xlsx</t>
+          <t>uar-netsuite-q2-2026.xlsx</t>
         </is>
       </c>
       <c r="C11" s="17" t="inlineStr">
         <is>
-          <t>Employees!D127 (Kevin Lewis)</t>
+          <t>Cover sheet — Observation 1 / Conclusion</t>
         </is>
       </c>
       <c r="D11" s="17" t="inlineStr">
         <is>
-          <t>HRIS record for Kevin Lewis shows employment status terminated, contradicting the retained decision.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="17" t="inlineStr">
-        <is>
-          <t>Inappropriate or excessive access identified during the review is remediated in a timely manner</t>
-        </is>
-      </c>
-      <c r="B12" s="17" t="inlineStr">
-        <is>
-          <t>uar-netsuite-q2-2026.xlsx</t>
-        </is>
-      </c>
-      <c r="C12" s="17" t="inlineStr">
-        <is>
-          <t>Cover sheet — Observation 1 / Conclusion</t>
-        </is>
-      </c>
-      <c r="D12" s="17" t="inlineStr">
-        <is>
-          <t>Only 1 observation raised (Danielle Goodwin) with remediation via ITSM-48217; no mention of Kevin Lewis or any other terminated-but-active user.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="17" t="inlineStr">
-        <is>
-          <t>Inappropriate or excessive access identified during the review is remediated in a timely manner</t>
-        </is>
-      </c>
-      <c r="B13" s="17" t="inlineStr">
-        <is>
-          <t>reperformance</t>
-        </is>
-      </c>
-      <c r="C13" s="17" t="inlineStr">
-        <is>
-          <t>reviewer_missed_findings (count=1)</t>
-        </is>
-      </c>
-      <c r="D13" s="17" t="inlineStr">
-        <is>
-          <t>Reconciliation flagged Kevin Lewis as terminated-in-HRIS but retained by the reviewer — a case of inappropriate access not identified and not remediated.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="17" t="inlineStr">
-        <is>
-          <t>Inappropriate or excessive access identified during the review is remediated in a timely manner</t>
-        </is>
-      </c>
-      <c r="B14" s="17" t="inlineStr">
-        <is>
-          <t>uar-netsuite-q2-2026.xlsx</t>
-        </is>
-      </c>
-      <c r="C14" s="17" t="inlineStr">
-        <is>
-          <t>Cover sheet — Observation 1 remediation text</t>
-        </is>
-      </c>
-      <c r="D14" s="17" t="inlineStr">
-        <is>
-          <t>Remediation for Danielle Goodwin is only a raised ticket (ITSM-48217, due within 5 business days); no evidence provided that the account was actually deprovisioned in NetSuite.</t>
+          <t>Only Danielle Goodwin was flagged for revocation via ITSM-48217 (due within 5 business days). Ticket raised but no completed remediation date is provided, and the account remained Active at time of export.</t>
         </is>
       </c>
     </row>
@@ -1384,7 +1345,7 @@
     <row r="4" ht="100" customHeight="1">
       <c r="A4" s="8" t="inlineStr">
         <is>
-          <t>System export: 334 rows | HRIS roster: 720 rows | Reviewer sheet: 334 rows | Matched to HRIS: 332 | Orphans (no HRIS record): 2 | Terminated but active in system: 2 | On leave but active in system: 8 | Reviewer missed (terminated + retained): 1</t>
+          <t>Full-population reperformance — 100% of the 334 in-scope account(s) tested, not a sample | System export: 334 rows | HRIS roster: 720 rows | Reviewer sheet: 334 rows | Matched to HRIS: 332 | Orphans (no HRIS record): 2 | Terminated but active in system: 2 | On leave but active in system: 8 | Reviewer missed (terminated + retained): 1</t>
         </is>
       </c>
     </row>
@@ -1459,9 +1420,9 @@
           <t>Workbook · 2 sheet(s), 720 rows total. Sheets: Employees, Notes</t>
         </is>
       </c>
-      <c r="E2" s="17" t="inlineStr">
-        <is>
-          <t>timely-remediation</t>
+      <c r="E2" s="22" t="inlineStr">
+        <is>
+          <t>— uncited —</t>
         </is>
       </c>
     </row>
@@ -1486,7 +1447,7 @@
       </c>
       <c r="E3" s="17" t="inlineStr">
         <is>
-          <t>periodic-review-cadence, periodic-review-cadence, periodic-review-cadence, periodic-review-cadence, reviewed-approved-by-owner, reviewed-approved-by-owner, reviewed-approved-by-owner, reviewed-approved-by-owner, timely-remediation, timely-remediation, timely-remediation</t>
+          <t>access-reviews-performed-periodically, access-reviews-performed-periodically, access-reviewed-approved-by-owner, access-reviewed-approved-by-owner, access-reviewed-approved-by-owner, inappropriate-access-remediated-timely, inappropriate-access-remediated-timely</t>
         </is>
       </c>
     </row>
@@ -1568,33 +1529,33 @@
       </c>
       <c r="B2" s="17" t="inlineStr">
         <is>
-          <t>2026-07-03T04:02:28.582885Z</t>
+          <t>2026-07-03T04:22:36.174533Z</t>
         </is>
       </c>
       <c r="C2" s="17" t="inlineStr">
         <is>
-          <t>judge:periodic-review-cadence:sample-1</t>
+          <t>judge:access-reviews-performed-periodically:sample-1</t>
         </is>
       </c>
       <c r="D2" s="17" t="inlineStr">
         <is>
-          <t>claude-opus-4-7</t>
+          <t>claude-opus-4-8</t>
         </is>
       </c>
       <c r="E2" s="17" t="n">
-        <v>26600</v>
+        <v>26231</v>
       </c>
       <c r="F2" s="17" t="n">
+        <v>5151</v>
+      </c>
+      <c r="G2" s="17" t="n">
+        <v>832</v>
+      </c>
+      <c r="H2" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="G2" s="17" t="n">
-        <v>940</v>
-      </c>
-      <c r="H2" s="22" t="n">
-        <v>0.48891375</v>
-      </c>
       <c r="I2" s="17" t="n">
-        <v>12379</v>
+        <v>13389</v>
       </c>
     </row>
     <row r="3">
@@ -1603,33 +1564,33 @@
       </c>
       <c r="B3" s="17" t="inlineStr">
         <is>
-          <t>2026-07-03T04:02:39.916718Z</t>
+          <t>2026-07-03T04:22:48.647418Z</t>
         </is>
       </c>
       <c r="C3" s="17" t="inlineStr">
         <is>
-          <t>judge:reviewed-approved-by-owner:sample-1</t>
+          <t>judge:access-reviewed-approved-by-owner:sample-1</t>
         </is>
       </c>
       <c r="D3" s="17" t="inlineStr">
         <is>
-          <t>claude-opus-4-7</t>
+          <t>claude-opus-4-8</t>
         </is>
       </c>
       <c r="E3" s="17" t="n">
-        <v>26647</v>
+        <v>26258</v>
       </c>
       <c r="F3" s="17" t="n">
-        <v>5177</v>
+        <v>5151</v>
       </c>
       <c r="G3" s="17" t="n">
-        <v>904</v>
-      </c>
-      <c r="H3" s="22" t="n">
-        <v>0.3976155</v>
+        <v>1017</v>
+      </c>
+      <c r="H3" s="23" t="n">
+        <v>0</v>
       </c>
       <c r="I3" s="17" t="n">
-        <v>11331</v>
+        <v>12469</v>
       </c>
     </row>
     <row r="4">
@@ -1638,58 +1599,58 @@
       </c>
       <c r="B4" s="17" t="inlineStr">
         <is>
-          <t>2026-07-03T04:02:58.039390Z</t>
+          <t>2026-07-03T04:23:01.959430Z</t>
         </is>
       </c>
       <c r="C4" s="17" t="inlineStr">
         <is>
-          <t>judge:timely-remediation:sample-1</t>
+          <t>judge:inappropriate-access-remediated-timely:sample-1</t>
         </is>
       </c>
       <c r="D4" s="17" t="inlineStr">
         <is>
-          <t>claude-opus-4-7</t>
+          <t>claude-opus-4-8</t>
         </is>
       </c>
       <c r="E4" s="17" t="n">
-        <v>26650</v>
+        <v>26254</v>
       </c>
       <c r="F4" s="17" t="n">
-        <v>5177</v>
+        <v>5151</v>
       </c>
       <c r="G4" s="17" t="n">
-        <v>1208</v>
-      </c>
-      <c r="H4" s="22" t="n">
-        <v>0.4204605</v>
+        <v>1007</v>
+      </c>
+      <c r="H4" s="23" t="n">
+        <v>0</v>
       </c>
       <c r="I4" s="17" t="n">
-        <v>18118</v>
+        <v>13303</v>
       </c>
     </row>
     <row r="5">
-      <c r="C5" s="23" t="inlineStr">
+      <c r="C5" s="24" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="E5" s="23">
+      <c r="E5" s="24">
         <f>SUM(E2:E4)</f>
         <v/>
       </c>
-      <c r="F5" s="23">
+      <c r="F5" s="24">
         <f>SUM(F2:F4)</f>
         <v/>
       </c>
-      <c r="G5" s="23">
+      <c r="G5" s="24">
         <f>SUM(G2:G4)</f>
         <v/>
       </c>
-      <c r="H5" s="24">
+      <c r="H5" s="25">
         <f>SUM(H2:H4)</f>
         <v/>
       </c>
-      <c r="I5" s="23">
+      <c r="I5" s="24">
         <f>SUM(I2:I4)</f>
         <v/>
       </c>
